--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6864C012-536E-4959-B711-1BE0C9BBC0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9F3BDA-F240-4349-96AC-EA1F43C2F11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>additives-fluids</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>/products/fluids/1.jpg</t>
+  </si>
+  <si>
+    <t>new</t>
   </si>
 </sst>
 </file>
@@ -661,6 +664,9 @@
       <c r="H2" t="s">
         <v>1</v>
       </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
@@ -690,6 +696,9 @@
       <c r="H3" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
@@ -719,6 +728,9 @@
       <c r="H4" t="s">
         <v>1</v>
       </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
@@ -748,6 +760,9 @@
       <c r="H5" t="s">
         <v>1</v>
       </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
@@ -777,6 +792,9 @@
       <c r="H6" t="s">
         <v>1</v>
       </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
@@ -805,6 +823,9 @@
       </c>
       <c r="H7" t="s">
         <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9F3BDA-F240-4349-96AC-EA1F43C2F11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20C1078-8FBD-474C-8EB8-EAF5AF2C851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>additives-fluids</t>
   </si>
@@ -83,9 +83,6 @@
     <t>ماكس 44 كبير</t>
   </si>
   <si>
-    <t>max 44 large</t>
-  </si>
-  <si>
     <t>محسن أداء الموتور</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>فواحه بي-04</t>
   </si>
   <si>
-    <t>air fresh B-04</t>
-  </si>
-  <si>
     <t>فواحه بي-05</t>
   </si>
   <si>
@@ -110,18 +104,6 @@
     <t>فواحه بي-08</t>
   </si>
   <si>
-    <t>air fresh B-05</t>
-  </si>
-  <si>
-    <t>air fresh B-06</t>
-  </si>
-  <si>
-    <t>air fresh B-07</t>
-  </si>
-  <si>
-    <t>air fresh B-08</t>
-  </si>
-  <si>
     <t>Refreshing car scent multi porpose</t>
   </si>
   <si>
@@ -129,6 +111,36 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/2.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/3.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/4.jpg</t>
+  </si>
+  <si>
+    <t>air fresh B-22</t>
+  </si>
+  <si>
+    <t>air fresh B-23</t>
+  </si>
+  <si>
+    <t>air fresh B-24</t>
+  </si>
+  <si>
+    <t>air fresh B-25</t>
+  </si>
+  <si>
+    <t>air fresh B-40</t>
+  </si>
+  <si>
+    <t>max 44 small</t>
   </si>
 </sst>
 </file>
@@ -641,16 +653,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>1300</v>
@@ -665,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -676,13 +688,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
       </c>
       <c r="E3">
         <v>230</v>
@@ -694,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -705,31 +717,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>1400</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -737,31 +749,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>1400</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s">
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -769,31 +781,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>1500</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="G6" t="s">
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -801,31 +813,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>1500</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="G7" t="s">
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20C1078-8FBD-474C-8EB8-EAF5AF2C851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386B250B-630E-43EC-A9CC-821F5937902B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>additives-fluids</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>max 44 small</t>
+  </si>
+  <si>
+    <t>زيت موتور 3000 كم</t>
+  </si>
+  <si>
+    <t>motor oil 3000 Km</t>
+  </si>
+  <si>
+    <t>/products/-fluids/oil-3.jpg</t>
   </si>
 </sst>
 </file>
@@ -729,7 +738,7 @@
         <v>22</v>
       </c>
       <c r="E4">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F4">
         <v>150</v>
@@ -761,7 +770,7 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F5">
         <v>160</v>
@@ -793,7 +802,7 @@
         <v>22</v>
       </c>
       <c r="E6">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="F6">
         <v>170</v>
@@ -825,7 +834,7 @@
         <v>22</v>
       </c>
       <c r="E7">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F7">
         <v>180</v>
@@ -844,7 +853,30 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H8" s="1"/>
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>1200</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H9" s="1"/>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386B250B-630E-43EC-A9CC-821F5937902B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6BFC2C-1E5D-40EC-8A0F-E0EC92AEC249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
   <si>
     <t>additives-fluids</t>
   </si>
   <si>
-    <t>/products/air-fresheners/p1.png</t>
-  </si>
-  <si>
     <t>air-fresheners</t>
   </si>
   <si>
@@ -77,70 +74,7 @@
     <t>name_ar</t>
   </si>
   <si>
-    <t>فواحه متعددة الأغراض</t>
-  </si>
-  <si>
-    <t>ماكس 44 كبير</t>
-  </si>
-  <si>
-    <t>محسن أداء الموتور</t>
-  </si>
-  <si>
-    <t>High performance motor additive</t>
-  </si>
-  <si>
-    <t>فواحه بي-04</t>
-  </si>
-  <si>
-    <t>فواحه بي-05</t>
-  </si>
-  <si>
-    <t>فواحه بي-06</t>
-  </si>
-  <si>
-    <t>فواحه بي-07</t>
-  </si>
-  <si>
-    <t>فواحه بي-08</t>
-  </si>
-  <si>
-    <t>Refreshing car scent multi porpose</t>
-  </si>
-  <si>
-    <t>/products/fluids/1.jpg</t>
-  </si>
-  <si>
     <t>new</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/2.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/3.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/4.jpg</t>
-  </si>
-  <si>
-    <t>air fresh B-22</t>
-  </si>
-  <si>
-    <t>air fresh B-23</t>
-  </si>
-  <si>
-    <t>air fresh B-24</t>
-  </si>
-  <si>
-    <t>air fresh B-25</t>
-  </si>
-  <si>
-    <t>air fresh B-40</t>
-  </si>
-  <si>
-    <t>max 44 small</t>
   </si>
   <si>
     <t>زيت موتور 3000 كم</t>
@@ -630,48 +564,48 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>1300</v>
@@ -680,13 +614,13 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -694,16 +628,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>230</v>
@@ -714,11 +648,11 @@
       <c r="G3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
+      <c r="H3" t="s">
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -726,16 +660,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>1500</v>
@@ -744,13 +678,13 @@
         <v>150</v>
       </c>
       <c r="G4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -758,16 +692,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>1600</v>
@@ -776,13 +710,13 @@
         <v>160</v>
       </c>
       <c r="G5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -790,16 +724,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>1700</v>
@@ -808,13 +742,13 @@
         <v>170</v>
       </c>
       <c r="G6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -822,16 +756,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>1800</v>
@@ -840,13 +774,13 @@
         <v>180</v>
       </c>
       <c r="G7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -854,16 +788,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>1200</v>
@@ -875,7 +809,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -930,9 +870,6 @@
       <c r="H25" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" display="public\products\fluids\1.jpg" xr:uid="{1E6D7678-44DB-4D0E-99B7-B5BDA146F84E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6BFC2C-1E5D-40EC-8A0F-E0EC92AEC249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722578F5-DB5E-4FB6-93AA-8874CB9CACAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
   <si>
     <t>additives-fluids</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>/products/-fluids/oil-3.jpg</t>
+  </si>
+  <si>
+    <t>/products/-fluids/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/-fluids/5.webp</t>
+  </si>
+  <si>
+    <t>/products/-fluids/oil-1.jpg</t>
+  </si>
+  <si>
+    <t>/products/-fluids/oil-2.jpg</t>
   </si>
 </sst>
 </file>
@@ -546,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EC3CDE-3A82-4D38-BD7C-286A991AD541}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -617,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -649,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -681,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -713,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -755,68 +767,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>1800</v>
-      </c>
-      <c r="F7">
-        <v>180</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>1200</v>
-      </c>
-      <c r="F8">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H9" s="1"/>
@@ -862,12 +816,6 @@
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722578F5-DB5E-4FB6-93AA-8874CB9CACAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD069BF-1773-4D9C-B02B-7833FE029BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -83,19 +83,19 @@
     <t>motor oil 3000 Km</t>
   </si>
   <si>
-    <t>/products/-fluids/oil-3.jpg</t>
-  </si>
-  <si>
-    <t>/products/-fluids/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/-fluids/5.webp</t>
-  </si>
-  <si>
-    <t>/products/-fluids/oil-1.jpg</t>
-  </si>
-  <si>
-    <t>/products/-fluids/oil-2.jpg</t>
+    <t>/products/fluids/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/fluids/5.webp</t>
+  </si>
+  <si>
+    <t>/products/fluids/oil-1.jpg</t>
+  </si>
+  <si>
+    <t>/products/fluids/oil-2.jpg</t>
+  </si>
+  <si>
+    <t>/products/fluids/oil-3.jpg</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -725,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD069BF-1773-4D9C-B02B-7833FE029BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88A4D94-7AC9-46AA-8DAC-53307D58EA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
-  <si>
-    <t>additives-fluids</t>
-  </si>
-  <si>
-    <t>air-fresheners</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>active</t>
   </si>
@@ -77,25 +71,52 @@
     <t>new</t>
   </si>
   <si>
-    <t>زيت موتور 3000 كم</t>
-  </si>
-  <si>
-    <t>motor oil 3000 Km</t>
-  </si>
-  <si>
-    <t>/products/fluids/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/fluids/5.webp</t>
-  </si>
-  <si>
-    <t>/products/fluids/oil-1.jpg</t>
-  </si>
-  <si>
-    <t>/products/fluids/oil-2.jpg</t>
-  </si>
-  <si>
-    <t>/products/fluids/oil-3.jpg</t>
+    <t>accessories</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 1</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 2</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 3</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 4</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 5</t>
+  </si>
+  <si>
+    <t>Mobile holder 1</t>
+  </si>
+  <si>
+    <t>Mobile holder 2</t>
+  </si>
+  <si>
+    <t>Mobile holder 3</t>
+  </si>
+  <si>
+    <t>Mobile holder 4</t>
+  </si>
+  <si>
+    <t>Mobile holder 5</t>
+  </si>
+  <si>
+    <t>/products/car-accessories/1.webp</t>
+  </si>
+  <si>
+    <t>/products/car-accessories/2.jpeg</t>
+  </si>
+  <si>
+    <t>/products/car-accessories/3.png</t>
+  </si>
+  <si>
+    <t>/products/car-accessories/4.png</t>
+  </si>
+  <si>
+    <t>/products/car-accessories/5.png</t>
   </si>
 </sst>
 </file>
@@ -558,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EC3CDE-3A82-4D38-BD7C-286A991AD541}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -568,232 +589,233 @@
     <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>1300</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="F4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="F5">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>1700</v>
+        <v>900</v>
       </c>
       <c r="F6">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G6" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.3">

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88A4D94-7AC9-46AA-8DAC-53307D58EA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B8BF0A-62B7-4E0B-B8F0-C1BEA98D241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -71,59 +71,59 @@
     <t>new</t>
   </si>
   <si>
-    <t>accessories</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 1</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 2</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 3</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 4</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 5</t>
-  </si>
-  <si>
-    <t>Mobile holder 1</t>
-  </si>
-  <si>
-    <t>Mobile holder 2</t>
-  </si>
-  <si>
-    <t>Mobile holder 3</t>
-  </si>
-  <si>
-    <t>Mobile holder 4</t>
-  </si>
-  <si>
-    <t>Mobile holder 5</t>
-  </si>
-  <si>
-    <t>/products/car-accessories/1.webp</t>
-  </si>
-  <si>
-    <t>/products/car-accessories/2.jpeg</t>
-  </si>
-  <si>
-    <t>/products/car-accessories/3.png</t>
-  </si>
-  <si>
-    <t>/products/car-accessories/4.png</t>
-  </si>
-  <si>
-    <t>/products/car-accessories/5.png</t>
+    <t>طقم ليد تيسلا اتش9</t>
+  </si>
+  <si>
+    <t>front led light H9</t>
+  </si>
+  <si>
+    <t>طقم ليد تيسلا اتش10</t>
+  </si>
+  <si>
+    <t>طقم ليد تيسلا اتش11</t>
+  </si>
+  <si>
+    <t>طقم ليد تيسلا اتش12</t>
+  </si>
+  <si>
+    <t>طقم ليد تيسلا اتش13</t>
+  </si>
+  <si>
+    <t>front led light H10</t>
+  </si>
+  <si>
+    <t>front led light H11</t>
+  </si>
+  <si>
+    <t>front led light H12</t>
+  </si>
+  <si>
+    <t>front led light H13</t>
+  </si>
+  <si>
+    <t>cars lights</t>
+  </si>
+  <si>
+    <t>/products/cars lights/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars lights/2.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars lights/3.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars lights/4.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars lights/5.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +135,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -629,25 +635,25 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
         <v>22</v>
@@ -665,22 +671,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>600</v>
+        <v>2601</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>23</v>
@@ -697,22 +703,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>700</v>
+        <v>2602</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -729,22 +735,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>800</v>
+        <v>2603</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -761,22 +767,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>2604</v>
+      </c>
+      <c r="F6">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
         <v>21</v>
-      </c>
-      <c r="E6">
-        <v>900</v>
-      </c>
-      <c r="F6">
-        <v>150</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
       </c>
       <c r="H6" t="s">
         <v>26</v>
@@ -840,6 +846,7 @@
       <c r="H23" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B8BF0A-62B7-4E0B-B8F0-C1BEA98D241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CDB797-5135-4886-95C9-5FAF3CFB9DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -104,19 +104,19 @@
     <t>cars lights</t>
   </si>
   <si>
-    <t>/products/cars lights/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars lights/2.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars lights/3.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars lights/4.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars lights/5.jpg</t>
+    <t>/products/Cars-lights/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/Cars-lights/2.jpg</t>
+  </si>
+  <si>
+    <t>/products/Cars-lights/3.jpg</t>
+  </si>
+  <si>
+    <t>/products/Cars-lights/4.jpg</t>
+  </si>
+  <si>
+    <t>/products/Cars-lights/5.jpg</t>
   </si>
 </sst>
 </file>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CDB797-5135-4886-95C9-5FAF3CFB9DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1598F40E-5977-4FEB-85A9-5C7BB4F2428C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -104,19 +104,19 @@
     <t>cars lights</t>
   </si>
   <si>
-    <t>/products/Cars-lights/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/Cars-lights/2.jpg</t>
-  </si>
-  <si>
-    <t>/products/Cars-lights/3.jpg</t>
-  </si>
-  <si>
-    <t>/products/Cars-lights/4.jpg</t>
-  </si>
-  <si>
-    <t>/products/Cars-lights/5.jpg</t>
+    <t>/products/cars-lights/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars-lights/2.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars-lights/3.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars-lights/4.jpg</t>
+  </si>
+  <si>
+    <t>/products/cars-lights/5.jpg</t>
   </si>
 </sst>
 </file>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1598F40E-5977-4FEB-85A9-5C7BB4F2428C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F555A48-381D-46AF-BB88-7CD68436B900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -101,22 +101,22 @@
     <t>front led light H13</t>
   </si>
   <si>
-    <t>cars lights</t>
-  </si>
-  <si>
-    <t>/products/cars-lights/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars-lights/2.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars-lights/3.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars-lights/4.jpg</t>
-  </si>
-  <si>
-    <t>/products/cars-lights/5.jpg</t>
+    <t>/products/air-fresheners/1.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/2.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/3.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/4.jpg</t>
+  </si>
+  <si>
+    <t>/products/air-fresheners/5.webp</t>
+  </si>
+  <si>
+    <t>air-freshener</t>
   </si>
 </sst>
 </file>
@@ -653,10 +653,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
         <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -686,10 +686,10 @@
         <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
@@ -718,10 +718,10 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -750,10 +750,10 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
@@ -782,10 +782,10 @@
         <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
@@ -848,5 +848,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F555A48-381D-46AF-BB88-7CD68436B900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66690881-E9BE-4C23-804E-29A3BF633D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -116,7 +116,7 @@
     <t>/products/air-fresheners/5.webp</t>
   </si>
   <si>
-    <t>air-freshener</t>
+    <t>air-fresheners</t>
   </si>
 </sst>
 </file>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66690881-E9BE-4C23-804E-29A3BF633D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1D82D8-C659-48CE-BE2D-F954891A254D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
   <si>
     <t>active</t>
   </si>
@@ -71,59 +71,47 @@
     <t>new</t>
   </si>
   <si>
-    <t>طقم ليد تيسلا اتش9</t>
-  </si>
-  <si>
-    <t>front led light H9</t>
-  </si>
-  <si>
-    <t>طقم ليد تيسلا اتش10</t>
-  </si>
-  <si>
-    <t>طقم ليد تيسلا اتش11</t>
-  </si>
-  <si>
-    <t>طقم ليد تيسلا اتش12</t>
-  </si>
-  <si>
-    <t>طقم ليد تيسلا اتش13</t>
-  </si>
-  <si>
-    <t>front led light H10</t>
-  </si>
-  <si>
-    <t>front led light H11</t>
-  </si>
-  <si>
-    <t>front led light H12</t>
-  </si>
-  <si>
-    <t>front led light H13</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/1.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/2.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/3.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/4.jpg</t>
-  </si>
-  <si>
-    <t>/products/air-fresheners/5.webp</t>
-  </si>
-  <si>
-    <t>air-fresheners</t>
+    <t>حامل موبايل للسيارة 1</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 2</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 3</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 4</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 5</t>
+  </si>
+  <si>
+    <t>mobile holder 1</t>
+  </si>
+  <si>
+    <t>mobile holder 2</t>
+  </si>
+  <si>
+    <t>mobile holder 3</t>
+  </si>
+  <si>
+    <t>mobile holder 4</t>
+  </si>
+  <si>
+    <t>mobile holder 5</t>
+  </si>
+  <si>
+    <t>accessories</t>
+  </si>
+  <si>
+    <t>/products/accessories/1.webp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +132,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -167,9 +161,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -588,7 +585,7 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
@@ -634,17 +631,17 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>2600</v>
@@ -653,10 +650,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -667,14 +664,14 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -686,7 +683,7 @@
         <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -699,14 +696,14 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -718,10 +715,10 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -731,14 +728,14 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -750,10 +747,10 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
@@ -763,14 +760,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>16</v>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -782,10 +779,10 @@
         <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1D82D8-C659-48CE-BE2D-F954891A254D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B79F0A3-586F-43CF-B16B-E14EB8FCA4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -71,40 +71,40 @@
     <t>new</t>
   </si>
   <si>
-    <t>حامل موبايل للسيارة 1</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 2</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 3</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 4</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 5</t>
-  </si>
-  <si>
-    <t>mobile holder 1</t>
-  </si>
-  <si>
-    <t>mobile holder 2</t>
-  </si>
-  <si>
-    <t>mobile holder 3</t>
-  </si>
-  <si>
-    <t>mobile holder 4</t>
-  </si>
-  <si>
-    <t>mobile holder 5</t>
-  </si>
-  <si>
-    <t>accessories</t>
-  </si>
-  <si>
     <t>/products/accessories/1.webp</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 7</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 8</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 9</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 10</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 11</t>
+  </si>
+  <si>
+    <t>mobile holder 7</t>
+  </si>
+  <si>
+    <t>mobile holder 8</t>
+  </si>
+  <si>
+    <t>mobile holder 9</t>
+  </si>
+  <si>
+    <t>mobile holder 10</t>
+  </si>
+  <si>
+    <t>mobile holder 11</t>
+  </si>
+  <si>
+    <t>equipment</t>
   </si>
 </sst>
 </file>
@@ -632,16 +632,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>2600</v>
@@ -650,10 +650,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -665,16 +665,16 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>2601</v>
@@ -683,10 +683,10 @@
         <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
@@ -697,16 +697,16 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>2602</v>
@@ -715,10 +715,10 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -729,16 +729,16 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>2603</v>
@@ -747,10 +747,10 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
@@ -761,16 +761,16 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>2604</v>
@@ -779,10 +779,10 @@
         <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B79F0A3-586F-43CF-B16B-E14EB8FCA4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E82F3F-5B47-406C-8752-9C4187CEAE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>active</t>
   </si>
@@ -74,37 +74,49 @@
     <t>/products/accessories/1.webp</t>
   </si>
   <si>
-    <t>حامل موبايل للسيارة 7</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 8</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 9</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 10</t>
-  </si>
-  <si>
-    <t>حامل موبايل للسيارة 11</t>
-  </si>
-  <si>
-    <t>mobile holder 7</t>
-  </si>
-  <si>
-    <t>mobile holder 8</t>
-  </si>
-  <si>
-    <t>mobile holder 9</t>
-  </si>
-  <si>
-    <t>mobile holder 10</t>
-  </si>
-  <si>
-    <t>mobile holder 11</t>
-  </si>
-  <si>
     <t>equipment</t>
+  </si>
+  <si>
+    <t>/products/accessories/2.jpeg</t>
+  </si>
+  <si>
+    <t>/products/accessories/3.png</t>
+  </si>
+  <si>
+    <t>/products/accessories/4.png</t>
+  </si>
+  <si>
+    <t>/products/accessories/5.png</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 1</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 2</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 3</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 4</t>
+  </si>
+  <si>
+    <t>حامل موبايل للسيارة 5</t>
+  </si>
+  <si>
+    <t>mobile holder 1</t>
+  </si>
+  <si>
+    <t>mobile holder 2</t>
+  </si>
+  <si>
+    <t>mobile holder 3</t>
+  </si>
+  <si>
+    <t>mobile holder 4</t>
+  </si>
+  <si>
+    <t>mobile holder 5</t>
   </si>
 </sst>
 </file>
@@ -632,25 +644,25 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>2600</v>
+        <v>600</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -665,31 +677,28 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>2601</v>
+        <v>700</v>
       </c>
       <c r="F3">
         <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -697,31 +706,28 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>2602</v>
+        <v>800</v>
       </c>
       <c r="F4">
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -729,31 +735,28 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>2603</v>
+        <v>900</v>
       </c>
       <c r="F5">
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -761,31 +764,28 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>2604</v>
+        <v>950</v>
       </c>
       <c r="F6">
         <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E82F3F-5B47-406C-8752-9C4187CEAE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48554A9-97BE-4048-B913-9157736D04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -71,24 +71,12 @@
     <t>new</t>
   </si>
   <si>
-    <t>/products/accessories/1.webp</t>
-  </si>
-  <si>
     <t>equipment</t>
   </si>
   <si>
     <t>/products/accessories/2.jpeg</t>
   </si>
   <si>
-    <t>/products/accessories/3.png</t>
-  </si>
-  <si>
-    <t>/products/accessories/4.png</t>
-  </si>
-  <si>
-    <t>/products/accessories/5.png</t>
-  </si>
-  <si>
     <t>حامل موبايل للسيارة 1</t>
   </si>
   <si>
@@ -117,6 +105,18 @@
   </si>
   <si>
     <t>mobile holder 5</t>
+  </si>
+  <si>
+    <t>/products/accessories/1.jpeg</t>
+  </si>
+  <si>
+    <t>/products/accessories/3.jpeg</t>
+  </si>
+  <si>
+    <t>/products/accessories/4.jpeg</t>
+  </si>
+  <si>
+    <t>/products/accessories/5.jpeg</t>
   </si>
 </sst>
 </file>
@@ -644,16 +644,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>600</v>
@@ -662,10 +662,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -677,16 +677,16 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>700</v>
@@ -695,10 +695,10 @@
         <v>101</v>
       </c>
       <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>800</v>
@@ -724,10 +724,10 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -735,16 +735,16 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>900</v>
@@ -753,10 +753,10 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -764,16 +764,16 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>950</v>
@@ -782,10 +782,10 @@
         <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>

--- a/trial 1.xlsx
+++ b/trial 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mohamed adel work\cesar-store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48554A9-97BE-4048-B913-9157736D04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093022E3-D5A1-4D92-A78E-64EE642AE510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{791D22A4-40A8-4DDB-9123-A17DB6BCCBDF}"/>
   </bookViews>
@@ -659,7 +659,7 @@
         <v>600</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -692,7 +692,7 @@
         <v>700</v>
       </c>
       <c r="F3">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -721,7 +721,7 @@
         <v>800</v>
       </c>
       <c r="F4">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -750,7 +750,7 @@
         <v>900</v>
       </c>
       <c r="F5">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -779,7 +779,7 @@
         <v>950</v>
       </c>
       <c r="F6">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
